--- a/artfynd/A 59793-2022 artfynd.xlsx
+++ b/artfynd/A 59793-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59793-2022 artfynd.xlsx
+++ b/artfynd/A 59793-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,68 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66370569</v>
+        <v>127501383</v>
       </c>
       <c r="B2" t="n">
-        <v>103164</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221137</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2600</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>väg 622, Jmt</t>
+          <t>Över-Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477387.8889593584</v>
+        <v>477371</v>
       </c>
       <c r="R2" t="n">
-        <v>6993072.461308611</v>
+        <v>6993039</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På östra sidan om vägen mellan Måläng och Rdömyren.</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingvar Alkemar</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingvar Alkemar</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110212075</v>
+        <v>127505175</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,38 +787,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klingermyren, Jmt</t>
+          <t>Över-Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477676.244168442</v>
+        <v>477370</v>
       </c>
       <c r="R3" t="n">
-        <v>6993214.182096391</v>
+        <v>6992997</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +865,454 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127505176</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Över-Måläng, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>477371</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6992992</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>66370569</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>väg 622, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>477388</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6993072</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-06-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-06-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På östra sidan om vägen mellan Måläng och Rdömyren.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ingvar Alkemar</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ingvar Alkemar</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127505177</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Över-Måläng, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477372</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6993014</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110212075</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Klingermyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477676</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6993214</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59793-2022 artfynd.xlsx
+++ b/artfynd/A 59793-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127505175</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127505176</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127505177</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66370569</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,8 +1343,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110212075</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>